--- a/Documentation/Best For Lists/Best Pets for Former Cat Owners List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Former Cat Owners List.xlsx
@@ -619,7 +619,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-12  |  Products shown: 4  |  Eliminated by dedup rule: 6  |  Pre-filter: Category equal Cat  (19 products removed)</t>
+          <t>Generated: 2026-07-15  |  Products shown: 4  |  Eliminated by dedup rule: 6  |  Pre-filter: Category equal Cat  (19 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Former Cat Owners List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Former Cat Owners List.xlsx
@@ -619,7 +619,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-15  |  Products shown: 4  |  Eliminated by dedup rule: 6  |  Pre-filter: Category equal Cat  (19 products removed)</t>
+          <t>Generated: 2026-07-16  |  Products shown: 4  |  Eliminated by dedup rule: 6  |  Pre-filter: Category equal Cat  (19 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Former Cat Owners List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Former Cat Owners List.xlsx
@@ -619,7 +619,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-16  |  Products shown: 4  |  Eliminated by dedup rule: 6  |  Pre-filter: Category equal Cat  (19 products removed)</t>
+          <t>Generated: 2026-08-10  |  Products shown: 4  |  Eliminated by dedup rule: 6  |  Pre-filter: Category equal Cat  (19 products removed)</t>
         </is>
       </c>
     </row>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>456</v>
+        <v>29</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>4.65</v>
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>5</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>4.35</v>
@@ -918,7 +918,7 @@
         <v>4.5</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>11640</v>
+        <v>12310</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>4.1</v>
@@ -961,7 +961,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>44.45</v>
+        <v>53.9</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>848</v>
+        <v>55</v>
       </c>
       <c r="I9" s="15" t="n">
         <v>2.8</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Previously scored as 'Calico Cat' — now matched to 'Grey Tabby Cat' per repo. Verify this is the correct product match before publishing. Review Strength=4: 848 reviews, 4.3★ (repo data, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. White coat: higher visual contrast against most furniture/bedding. Product name updated: 'Original Plush White Cat' per repo. Review Strength=2: 54 reviews, 4.0★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
         <v>4.15</v>
       </c>
       <c r="F4" s="18" t="n">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="G4" s="18" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H4" s="18" t="inlineStr">
         <is>
-          <t>score=4.15 rating=4</t>
+          <t>score=4.15 rating=4.95</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Original Siamese Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -1269,16 +1269,16 @@
         <v>2.8</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>score=2.80 rating=4.1</t>
+          <t>score=2.80 rating=4.2</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Original Plush White Cat</t>
+          <t>Original Siamese Cat</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
@@ -1307,16 +1307,16 @@
         <v>2.8</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="H8" s="18" t="inlineStr">
         <is>
-          <t>score=2.80 rating=4</t>
+          <t>score=2.80 rating=4.1</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Former Cat Owners List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Former Cat Owners List.xlsx
@@ -619,7 +619,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-10  |  Products shown: 4  |  Eliminated by dedup rule: 6  |  Pre-filter: Category equal Cat  (19 products removed)</t>
+          <t>Generated: 2026-08-13  |  Products shown: 4  |  Eliminated by dedup rule: 6  |  Pre-filter: Category equal Cat  (19 products removed)</t>
         </is>
       </c>
     </row>
